--- a/results/04_final_refined_daily_hydroclimate_data/508/Wet_bulb_temp_06h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/508/Wet_bulb_temp_06h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -456,7 +456,7 @@
         <v>4</v>
       </c>
       <c r="D5">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -567,8 +567,8 @@
       <c r="C13">
         <v>12</v>
       </c>
-      <c r="D13">
-        <v>18.2</v>
+      <c r="D13" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -581,8 +581,8 @@
       <c r="C14">
         <v>13</v>
       </c>
-      <c r="D14">
-        <v>19.2</v>
+      <c r="D14" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -609,8 +609,8 @@
       <c r="C16">
         <v>15</v>
       </c>
-      <c r="D16">
-        <v>18</v>
+      <c r="D16" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/508/Wet_bulb_temp_06h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/508/Wet_bulb_temp_06h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -567,8 +567,8 @@
       <c r="C13">
         <v>12</v>
       </c>
-      <c r="D13" t="s">
-        <v>4</v>
+      <c r="D13">
+        <v>18.2</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -581,8 +581,8 @@
       <c r="C14">
         <v>13</v>
       </c>
-      <c r="D14" t="s">
-        <v>4</v>
+      <c r="D14">
+        <v>19.2</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -609,8 +609,8 @@
       <c r="C16">
         <v>15</v>
       </c>
-      <c r="D16" t="s">
-        <v>4</v>
+      <c r="D16">
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -623,8 +623,8 @@
       <c r="C17">
         <v>16</v>
       </c>
-      <c r="D17" t="s">
-        <v>4</v>
+      <c r="D17">
+        <v>19.1</v>
       </c>
     </row>
     <row r="18" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/508/Wet_bulb_temp_06h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/508/Wet_bulb_temp_06h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -553,8 +553,8 @@
       <c r="C12">
         <v>11</v>
       </c>
-      <c r="D12" t="s">
-        <v>4</v>
+      <c r="D12">
+        <v>19.6</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -595,8 +595,8 @@
       <c r="C15">
         <v>14</v>
       </c>
-      <c r="D15" t="s">
-        <v>4</v>
+      <c r="D15">
+        <v>18.4</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -623,8 +623,8 @@
       <c r="C17">
         <v>16</v>
       </c>
-      <c r="D17">
-        <v>19.1</v>
+      <c r="D17" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/508/Wet_bulb_temp_06h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/508/Wet_bulb_temp_06h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -483,8 +483,8 @@
       <c r="C7">
         <v>6</v>
       </c>
-      <c r="D7" t="s">
-        <v>4</v>
+      <c r="D7">
+        <v>19.3</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -497,8 +497,8 @@
       <c r="C8">
         <v>7</v>
       </c>
-      <c r="D8" t="s">
-        <v>4</v>
+      <c r="D8">
+        <v>18.8</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -511,8 +511,8 @@
       <c r="C9">
         <v>8</v>
       </c>
-      <c r="D9" t="s">
-        <v>4</v>
+      <c r="D9">
+        <v>18.9</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -525,8 +525,8 @@
       <c r="C10">
         <v>9</v>
       </c>
-      <c r="D10" t="s">
-        <v>4</v>
+      <c r="D10">
+        <v>18.7</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -539,8 +539,8 @@
       <c r="C11">
         <v>10</v>
       </c>
-      <c r="D11" t="s">
-        <v>4</v>
+      <c r="D11">
+        <v>18.9</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -553,8 +553,8 @@
       <c r="C12">
         <v>11</v>
       </c>
-      <c r="D12">
-        <v>19.6</v>
+      <c r="D12" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -567,8 +567,8 @@
       <c r="C13">
         <v>12</v>
       </c>
-      <c r="D13">
-        <v>18.2</v>
+      <c r="D13" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -581,8 +581,8 @@
       <c r="C14">
         <v>13</v>
       </c>
-      <c r="D14">
-        <v>19.2</v>
+      <c r="D14" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -595,8 +595,8 @@
       <c r="C15">
         <v>14</v>
       </c>
-      <c r="D15">
-        <v>18.4</v>
+      <c r="D15" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -609,8 +609,8 @@
       <c r="C16">
         <v>15</v>
       </c>
-      <c r="D16">
-        <v>18</v>
+      <c r="D16" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -623,8 +623,8 @@
       <c r="C17">
         <v>16</v>
       </c>
-      <c r="D17" t="s">
-        <v>4</v>
+      <c r="D17">
+        <v>19.1</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -651,8 +651,8 @@
       <c r="C19">
         <v>18</v>
       </c>
-      <c r="D19" t="s">
-        <v>4</v>
+      <c r="D19">
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -763,8 +763,8 @@
       <c r="C27">
         <v>26</v>
       </c>
-      <c r="D27" t="s">
-        <v>4</v>
+      <c r="D27">
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -777,8 +777,8 @@
       <c r="C28">
         <v>27</v>
       </c>
-      <c r="D28" t="s">
-        <v>4</v>
+      <c r="D28">
+        <v>18.8</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -791,8 +791,8 @@
       <c r="C29">
         <v>28</v>
       </c>
-      <c r="D29" t="s">
-        <v>4</v>
+      <c r="D29">
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -805,8 +805,8 @@
       <c r="C30">
         <v>29</v>
       </c>
-      <c r="D30" t="s">
-        <v>4</v>
+      <c r="D30">
+        <v>19.3</v>
       </c>
     </row>
   </sheetData>
